--- a/strategy_packs/pullback_senales.xlsx
+++ b/strategy_packs/pullback_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fuerza_relativa_52w</t>
+          <t>rsi_señal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fuerza relativa 52 semanas</t>
+          <t>RSI señal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Premia a los activos que le vienen ganando a su benchmark en la ventana de 52 semanas: &gt;20 puntos de ventaja → 100; positivo → 50; resto → −50.</t>
+          <t>RSI diario invertido: sobreventa puntua positivo (RSI &lt;30 -&gt; 100) y sobrecompra negativo (&gt;70 -&gt; -100).</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -482,7 +482,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>relative_strength_52w</t>
+          <t>rsi_daily</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -492,24 +492,24 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
+          <t>{"thresholds": [[70, -100], [55, -50], [45, 0], [30, 50], [null, 100]]}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dist_sma_pullback_d</t>
+          <t>fuerza_relativa_52w</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Distancia a SMA óptima invertida (pullback)</t>
+          <t>Fuerza relativa 52 semanas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Versión invertida de dist_sma_d: premia estar CERCA o DEBAJO de la SMA óptima diaria (retroceso hacia soporte). 2 desvíos arriba → −100; 2 abajo → +100.</t>
+          <t>Premia a los activos que le vienen ganando a su benchmark en la ventana de 52 semanas: &gt;20 puntos de ventaja -&gt; 100; positivo -&gt; 50; resto -&gt; -50.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,17 +520,93 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
+          <t>relative_strength_52w</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dist_sma_pullback_d</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Distancia a SMA óptima invertida (pullback)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Version invertida de dist_sma_d: premia estar CERCA o DEBAJO de la SMA optima diaria (retroceso hacia soporte). 2 desvios arriba -&gt; -100; 2 abajo -&gt; +100.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>dist_optimal_sma_daily</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>range</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>{"min": 2.0, "max": -2.0, "clamp": true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tendencia_d</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tendencia diaria</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mapa del regimen de tendencia diario a score (alcista fuerte 100 ... bajista fuerte -100).</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>trend_daily</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
         </is>
       </c>
     </row>

--- a/strategy_packs/pullback_senales.xlsx
+++ b/strategy_packs/pullback_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>params</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>publica</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,7 +484,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>rsi_daily</t>
@@ -493,6 +497,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>{"thresholds": [[70, -100], [55, -50], [45, 0], [30, 50], [null, 100]]}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -517,7 +526,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>relative_strength_52w</t>
@@ -531,6 +539,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -555,7 +568,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>dist_optimal_sma_daily</t>
@@ -569,6 +581,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>{"min": 2.0, "max": -2.0, "clamp": true}</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
@@ -593,7 +610,6 @@
           <t>asset</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>trend_daily</t>
@@ -607,6 +623,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>

--- a/strategy_packs/pullback_senales.xlsx
+++ b/strategy_packs/pullback_senales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,30 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>indicator_key</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>group_type</t>
+          <t>formula_type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>indicator_key</t>
+          <t>params</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>formula_type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>params</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>publica</t>
         </is>
@@ -481,25 +471,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>rsi_daily</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>threshold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>rsi_daily</t>
+          <t>{"thresholds": [[70, -100], [55, -50], [45, 0], [30, 50], [null, 100]]}</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>{"thresholds": [[70, -100], [55, -50], [45, 0], [30, 50], [null, 100]]}</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -523,25 +508,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>relative_strength_52w</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>threshold</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>relative_strength_52w</t>
+          <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>{"thresholds": [[20, 100], [0, 50], [null, -50]]}</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -565,25 +545,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>dist_optimal_sma_daily</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>range</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>dist_optimal_sma_daily</t>
+          <t>{"min": 2.0, "max": -2.0, "clamp": true}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>{"min": 2.0, "max": -2.0, "clamp": true}</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -607,25 +582,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>trend_daily</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>discrete_map</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>trend_daily</t>
+          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>discrete_map</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>{"map": {"bullish_strong": 100, "bullish_nascent_strong": 75, "bullish": 60, "bullish_nascent": 40, "lateral_nascent": 5, "lateral": 0, "bearish_nascent": -40, "bearish_nascent_strong": -75, "bearish": -60, "bearish_strong": -100}}</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
